--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_14-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_14-10-2025.xlsx
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7391ae955+80021]
-	GetHandleVerifier [0x0x7ff7391ae9b0+80112]
-	(No symbol) [0x0x7ff738f3060f]
-	(No symbol) [0x0x7ff738f88854]
-	(No symbol) [0x0x7ff738f88b1c]
-	(No symbol) [0x0x7ff738fdc927]
-	(No symbol) [0x0x7ff738fb126f]
-	(No symbol) [0x0x7ff738fd968a]
-	(No symbol) [0x0x7ff738fb1003]
-	(No symbol) [0x0x7ff738f795d1]
-	(No symbol) [0x0x7ff738f7a3f3]
-	GetHandleVerifier [0x0x7ff73946dd0d+2960461]
-	GetHandleVerifier [0x0x7ff739467fca+2936586]
-	GetHandleVerifier [0x0x7ff739488a07+3070279]
-	GetHandleVerifier [0x0x7ff7391c843e+185214]
-	GetHandleVerifier [0x0x7ff7391cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7391b7b94+117460]
-	GetHandleVerifier [0x0x7ff7391b7d4f+117903]
-	GetHandleVerifier [0x0x7ff73919dc28+11112]
+	GetHandleVerifier [0x0x7ff7e437e955+80021]
+	GetHandleVerifier [0x0x7ff7e437e9b0+80112]
+	(No symbol) [0x0x7ff7e410060f]
+	(No symbol) [0x0x7ff7e4158854]
+	(No symbol) [0x0x7ff7e4158b1c]
+	(No symbol) [0x0x7ff7e41ac927]
+	(No symbol) [0x0x7ff7e418126f]
+	(No symbol) [0x0x7ff7e41a968a]
+	(No symbol) [0x0x7ff7e4181003]
+	(No symbol) [0x0x7ff7e41495d1]
+	(No symbol) [0x0x7ff7e414a3f3]
+	GetHandleVerifier [0x0x7ff7e463dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7e4637fca+2936586]
+	GetHandleVerifier [0x0x7ff7e4658a07+3070279]
+	GetHandleVerifier [0x0x7ff7e439843e+185214]
+	GetHandleVerifier [0x0x7ff7e439fe8f+216527]
+	GetHandleVerifier [0x0x7ff7e4387b94+117460]
+	GetHandleVerifier [0x0x7ff7e4387d4f+117903]
+	GetHandleVerifier [0x0x7ff7e436dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7391ae955+80021]
-	GetHandleVerifier [0x0x7ff7391ae9b0+80112]
-	(No symbol) [0x0x7ff738f3060f]
-	(No symbol) [0x0x7ff738f88854]
-	(No symbol) [0x0x7ff738f88b1c]
-	(No symbol) [0x0x7ff738fdc927]
-	(No symbol) [0x0x7ff738fb126f]
-	(No symbol) [0x0x7ff738fd968a]
-	(No symbol) [0x0x7ff738fb1003]
-	(No symbol) [0x0x7ff738f795d1]
-	(No symbol) [0x0x7ff738f7a3f3]
-	GetHandleVerifier [0x0x7ff73946dd0d+2960461]
-	GetHandleVerifier [0x0x7ff739467fca+2936586]
-	GetHandleVerifier [0x0x7ff739488a07+3070279]
-	GetHandleVerifier [0x0x7ff7391c843e+185214]
-	GetHandleVerifier [0x0x7ff7391cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7391b7b94+117460]
-	GetHandleVerifier [0x0x7ff7391b7d4f+117903]
-	GetHandleVerifier [0x0x7ff73919dc28+11112]
+	GetHandleVerifier [0x0x7ff7e437e955+80021]
+	GetHandleVerifier [0x0x7ff7e437e9b0+80112]
+	(No symbol) [0x0x7ff7e410060f]
+	(No symbol) [0x0x7ff7e4158854]
+	(No symbol) [0x0x7ff7e4158b1c]
+	(No symbol) [0x0x7ff7e41ac927]
+	(No symbol) [0x0x7ff7e418126f]
+	(No symbol) [0x0x7ff7e41a968a]
+	(No symbol) [0x0x7ff7e4181003]
+	(No symbol) [0x0x7ff7e41495d1]
+	(No symbol) [0x0x7ff7e414a3f3]
+	GetHandleVerifier [0x0x7ff7e463dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7e4637fca+2936586]
+	GetHandleVerifier [0x0x7ff7e4658a07+3070279]
+	GetHandleVerifier [0x0x7ff7e439843e+185214]
+	GetHandleVerifier [0x0x7ff7e439fe8f+216527]
+	GetHandleVerifier [0x0x7ff7e4387b94+117460]
+	GetHandleVerifier [0x0x7ff7e4387d4f+117903]
+	GetHandleVerifier [0x0x7ff7e436dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7391ae955+80021]
-	GetHandleVerifier [0x0x7ff7391ae9b0+80112]
-	(No symbol) [0x0x7ff738f3060f]
-	(No symbol) [0x0x7ff738f88854]
-	(No symbol) [0x0x7ff738f88b1c]
-	(No symbol) [0x0x7ff738fdc927]
-	(No symbol) [0x0x7ff738fb126f]
-	(No symbol) [0x0x7ff738fd968a]
-	(No symbol) [0x0x7ff738fb1003]
-	(No symbol) [0x0x7ff738f795d1]
-	(No symbol) [0x0x7ff738f7a3f3]
-	GetHandleVerifier [0x0x7ff73946dd0d+2960461]
-	GetHandleVerifier [0x0x7ff739467fca+2936586]
-	GetHandleVerifier [0x0x7ff739488a07+3070279]
-	GetHandleVerifier [0x0x7ff7391c843e+185214]
-	GetHandleVerifier [0x0x7ff7391cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7391b7b94+117460]
-	GetHandleVerifier [0x0x7ff7391b7d4f+117903]
-	GetHandleVerifier [0x0x7ff73919dc28+11112]
+	GetHandleVerifier [0x0x7ff7e437e955+80021]
+	GetHandleVerifier [0x0x7ff7e437e9b0+80112]
+	(No symbol) [0x0x7ff7e410060f]
+	(No symbol) [0x0x7ff7e4158854]
+	(No symbol) [0x0x7ff7e4158b1c]
+	(No symbol) [0x0x7ff7e41ac927]
+	(No symbol) [0x0x7ff7e418126f]
+	(No symbol) [0x0x7ff7e41a968a]
+	(No symbol) [0x0x7ff7e4181003]
+	(No symbol) [0x0x7ff7e41495d1]
+	(No symbol) [0x0x7ff7e414a3f3]
+	GetHandleVerifier [0x0x7ff7e463dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7e4637fca+2936586]
+	GetHandleVerifier [0x0x7ff7e4658a07+3070279]
+	GetHandleVerifier [0x0x7ff7e439843e+185214]
+	GetHandleVerifier [0x0x7ff7e439fe8f+216527]
+	GetHandleVerifier [0x0x7ff7e4387b94+117460]
+	GetHandleVerifier [0x0x7ff7e4387d4f+117903]
+	GetHandleVerifier [0x0x7ff7e436dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7391ae955+80021]
-	GetHandleVerifier [0x0x7ff7391ae9b0+80112]
-	(No symbol) [0x0x7ff738f3060f]
-	(No symbol) [0x0x7ff738f88854]
-	(No symbol) [0x0x7ff738f88b1c]
-	(No symbol) [0x0x7ff738fdc927]
-	(No symbol) [0x0x7ff738fb126f]
-	(No symbol) [0x0x7ff738fd968a]
-	(No symbol) [0x0x7ff738fb1003]
-	(No symbol) [0x0x7ff738f795d1]
-	(No symbol) [0x0x7ff738f7a3f3]
-	GetHandleVerifier [0x0x7ff73946dd0d+2960461]
-	GetHandleVerifier [0x0x7ff739467fca+2936586]
-	GetHandleVerifier [0x0x7ff739488a07+3070279]
-	GetHandleVerifier [0x0x7ff7391c843e+185214]
-	GetHandleVerifier [0x0x7ff7391cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7391b7b94+117460]
-	GetHandleVerifier [0x0x7ff7391b7d4f+117903]
-	GetHandleVerifier [0x0x7ff73919dc28+11112]
+	GetHandleVerifier [0x0x7ff7e437e955+80021]
+	GetHandleVerifier [0x0x7ff7e437e9b0+80112]
+	(No symbol) [0x0x7ff7e410060f]
+	(No symbol) [0x0x7ff7e4158854]
+	(No symbol) [0x0x7ff7e4158b1c]
+	(No symbol) [0x0x7ff7e41ac927]
+	(No symbol) [0x0x7ff7e418126f]
+	(No symbol) [0x0x7ff7e41a968a]
+	(No symbol) [0x0x7ff7e4181003]
+	(No symbol) [0x0x7ff7e41495d1]
+	(No symbol) [0x0x7ff7e414a3f3]
+	GetHandleVerifier [0x0x7ff7e463dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7e4637fca+2936586]
+	GetHandleVerifier [0x0x7ff7e4658a07+3070279]
+	GetHandleVerifier [0x0x7ff7e439843e+185214]
+	GetHandleVerifier [0x0x7ff7e439fe8f+216527]
+	GetHandleVerifier [0x0x7ff7e4387b94+117460]
+	GetHandleVerifier [0x0x7ff7e4387d4f+117903]
+	GetHandleVerifier [0x0x7ff7e436dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7391ae955+80021]
-	GetHandleVerifier [0x0x7ff7391ae9b0+80112]
-	(No symbol) [0x0x7ff738f3060f]
-	(No symbol) [0x0x7ff738f88854]
-	(No symbol) [0x0x7ff738f88b1c]
-	(No symbol) [0x0x7ff738fdc927]
-	(No symbol) [0x0x7ff738fb126f]
-	(No symbol) [0x0x7ff738fd968a]
-	(No symbol) [0x0x7ff738fb1003]
-	(No symbol) [0x0x7ff738f795d1]
-	(No symbol) [0x0x7ff738f7a3f3]
-	GetHandleVerifier [0x0x7ff73946dd0d+2960461]
-	GetHandleVerifier [0x0x7ff739467fca+2936586]
-	GetHandleVerifier [0x0x7ff739488a07+3070279]
-	GetHandleVerifier [0x0x7ff7391c843e+185214]
-	GetHandleVerifier [0x0x7ff7391cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7391b7b94+117460]
-	GetHandleVerifier [0x0x7ff7391b7d4f+117903]
-	GetHandleVerifier [0x0x7ff73919dc28+11112]
+	GetHandleVerifier [0x0x7ff7e437e955+80021]
+	GetHandleVerifier [0x0x7ff7e437e9b0+80112]
+	(No symbol) [0x0x7ff7e410060f]
+	(No symbol) [0x0x7ff7e4158854]
+	(No symbol) [0x0x7ff7e4158b1c]
+	(No symbol) [0x0x7ff7e41ac927]
+	(No symbol) [0x0x7ff7e418126f]
+	(No symbol) [0x0x7ff7e41a968a]
+	(No symbol) [0x0x7ff7e4181003]
+	(No symbol) [0x0x7ff7e41495d1]
+	(No symbol) [0x0x7ff7e414a3f3]
+	GetHandleVerifier [0x0x7ff7e463dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7e4637fca+2936586]
+	GetHandleVerifier [0x0x7ff7e4658a07+3070279]
+	GetHandleVerifier [0x0x7ff7e439843e+185214]
+	GetHandleVerifier [0x0x7ff7e439fe8f+216527]
+	GetHandleVerifier [0x0x7ff7e4387b94+117460]
+	GetHandleVerifier [0x0x7ff7e4387d4f+117903]
+	GetHandleVerifier [0x0x7ff7e436dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7391ae955+80021]
-	GetHandleVerifier [0x0x7ff7391ae9b0+80112]
-	(No symbol) [0x0x7ff738f3060f]
-	(No symbol) [0x0x7ff738f88854]
-	(No symbol) [0x0x7ff738f88b1c]
-	(No symbol) [0x0x7ff738fdc927]
-	(No symbol) [0x0x7ff738fb126f]
-	(No symbol) [0x0x7ff738fd968a]
-	(No symbol) [0x0x7ff738fb1003]
-	(No symbol) [0x0x7ff738f795d1]
-	(No symbol) [0x0x7ff738f7a3f3]
-	GetHandleVerifier [0x0x7ff73946dd0d+2960461]
-	GetHandleVerifier [0x0x7ff739467fca+2936586]
-	GetHandleVerifier [0x0x7ff739488a07+3070279]
-	GetHandleVerifier [0x0x7ff7391c843e+185214]
-	GetHandleVerifier [0x0x7ff7391cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7391b7b94+117460]
-	GetHandleVerifier [0x0x7ff7391b7d4f+117903]
-	GetHandleVerifier [0x0x7ff73919dc28+11112]
+	GetHandleVerifier [0x0x7ff7e437e955+80021]
+	GetHandleVerifier [0x0x7ff7e437e9b0+80112]
+	(No symbol) [0x0x7ff7e410060f]
+	(No symbol) [0x0x7ff7e4158854]
+	(No symbol) [0x0x7ff7e4158b1c]
+	(No symbol) [0x0x7ff7e41ac927]
+	(No symbol) [0x0x7ff7e418126f]
+	(No symbol) [0x0x7ff7e41a968a]
+	(No symbol) [0x0x7ff7e4181003]
+	(No symbol) [0x0x7ff7e41495d1]
+	(No symbol) [0x0x7ff7e414a3f3]
+	GetHandleVerifier [0x0x7ff7e463dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7e4637fca+2936586]
+	GetHandleVerifier [0x0x7ff7e4658a07+3070279]
+	GetHandleVerifier [0x0x7ff7e439843e+185214]
+	GetHandleVerifier [0x0x7ff7e439fe8f+216527]
+	GetHandleVerifier [0x0x7ff7e4387b94+117460]
+	GetHandleVerifier [0x0x7ff7e4387d4f+117903]
+	GetHandleVerifier [0x0x7ff7e436dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7391ae955+80021]
-	GetHandleVerifier [0x0x7ff7391ae9b0+80112]
-	(No symbol) [0x0x7ff738f3060f]
-	(No symbol) [0x0x7ff738f88854]
-	(No symbol) [0x0x7ff738f88b1c]
-	(No symbol) [0x0x7ff738fdc927]
-	(No symbol) [0x0x7ff738fb126f]
-	(No symbol) [0x0x7ff738fd968a]
-	(No symbol) [0x0x7ff738fb1003]
-	(No symbol) [0x0x7ff738f795d1]
-	(No symbol) [0x0x7ff738f7a3f3]
-	GetHandleVerifier [0x0x7ff73946dd0d+2960461]
-	GetHandleVerifier [0x0x7ff739467fca+2936586]
-	GetHandleVerifier [0x0x7ff739488a07+3070279]
-	GetHandleVerifier [0x0x7ff7391c843e+185214]
-	GetHandleVerifier [0x0x7ff7391cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7391b7b94+117460]
-	GetHandleVerifier [0x0x7ff7391b7d4f+117903]
-	GetHandleVerifier [0x0x7ff73919dc28+11112]
+	GetHandleVerifier [0x0x7ff7e437e955+80021]
+	GetHandleVerifier [0x0x7ff7e437e9b0+80112]
+	(No symbol) [0x0x7ff7e410060f]
+	(No symbol) [0x0x7ff7e4158854]
+	(No symbol) [0x0x7ff7e4158b1c]
+	(No symbol) [0x0x7ff7e41ac927]
+	(No symbol) [0x0x7ff7e418126f]
+	(No symbol) [0x0x7ff7e41a968a]
+	(No symbol) [0x0x7ff7e4181003]
+	(No symbol) [0x0x7ff7e41495d1]
+	(No symbol) [0x0x7ff7e414a3f3]
+	GetHandleVerifier [0x0x7ff7e463dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7e4637fca+2936586]
+	GetHandleVerifier [0x0x7ff7e4658a07+3070279]
+	GetHandleVerifier [0x0x7ff7e439843e+185214]
+	GetHandleVerifier [0x0x7ff7e439fe8f+216527]
+	GetHandleVerifier [0x0x7ff7e4387b94+117460]
+	GetHandleVerifier [0x0x7ff7e4387d4f+117903]
+	GetHandleVerifier [0x0x7ff7e436dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7391ae955+80021]
-	GetHandleVerifier [0x0x7ff7391ae9b0+80112]
-	(No symbol) [0x0x7ff738f3060f]
-	(No symbol) [0x0x7ff738f88854]
-	(No symbol) [0x0x7ff738f88b1c]
-	(No symbol) [0x0x7ff738fdc927]
-	(No symbol) [0x0x7ff738fb126f]
-	(No symbol) [0x0x7ff738fd968a]
-	(No symbol) [0x0x7ff738fb1003]
-	(No symbol) [0x0x7ff738f795d1]
-	(No symbol) [0x0x7ff738f7a3f3]
-	GetHandleVerifier [0x0x7ff73946dd0d+2960461]
-	GetHandleVerifier [0x0x7ff739467fca+2936586]
-	GetHandleVerifier [0x0x7ff739488a07+3070279]
-	GetHandleVerifier [0x0x7ff7391c843e+185214]
-	GetHandleVerifier [0x0x7ff7391cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7391b7b94+117460]
-	GetHandleVerifier [0x0x7ff7391b7d4f+117903]
-	GetHandleVerifier [0x0x7ff73919dc28+11112]
+	GetHandleVerifier [0x0x7ff7e437e955+80021]
+	GetHandleVerifier [0x0x7ff7e437e9b0+80112]
+	(No symbol) [0x0x7ff7e410060f]
+	(No symbol) [0x0x7ff7e4158854]
+	(No symbol) [0x0x7ff7e4158b1c]
+	(No symbol) [0x0x7ff7e41ac927]
+	(No symbol) [0x0x7ff7e418126f]
+	(No symbol) [0x0x7ff7e41a968a]
+	(No symbol) [0x0x7ff7e4181003]
+	(No symbol) [0x0x7ff7e41495d1]
+	(No symbol) [0x0x7ff7e414a3f3]
+	GetHandleVerifier [0x0x7ff7e463dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7e4637fca+2936586]
+	GetHandleVerifier [0x0x7ff7e4658a07+3070279]
+	GetHandleVerifier [0x0x7ff7e439843e+185214]
+	GetHandleVerifier [0x0x7ff7e439fe8f+216527]
+	GetHandleVerifier [0x0x7ff7e4387b94+117460]
+	GetHandleVerifier [0x0x7ff7e4387d4f+117903]
+	GetHandleVerifier [0x0x7ff7e436dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7391ae955+80021]
-	GetHandleVerifier [0x0x7ff7391ae9b0+80112]
-	(No symbol) [0x0x7ff738f3060f]
-	(No symbol) [0x0x7ff738f88854]
-	(No symbol) [0x0x7ff738f88b1c]
-	(No symbol) [0x0x7ff738fdc927]
-	(No symbol) [0x0x7ff738fb126f]
-	(No symbol) [0x0x7ff738fd968a]
-	(No symbol) [0x0x7ff738fb1003]
-	(No symbol) [0x0x7ff738f795d1]
-	(No symbol) [0x0x7ff738f7a3f3]
-	GetHandleVerifier [0x0x7ff73946dd0d+2960461]
-	GetHandleVerifier [0x0x7ff739467fca+2936586]
-	GetHandleVerifier [0x0x7ff739488a07+3070279]
-	GetHandleVerifier [0x0x7ff7391c843e+185214]
-	GetHandleVerifier [0x0x7ff7391cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7391b7b94+117460]
-	GetHandleVerifier [0x0x7ff7391b7d4f+117903]
-	GetHandleVerifier [0x0x7ff73919dc28+11112]
+	GetHandleVerifier [0x0x7ff7e437e955+80021]
+	GetHandleVerifier [0x0x7ff7e437e9b0+80112]
+	(No symbol) [0x0x7ff7e410060f]
+	(No symbol) [0x0x7ff7e4158854]
+	(No symbol) [0x0x7ff7e4158b1c]
+	(No symbol) [0x0x7ff7e41ac927]
+	(No symbol) [0x0x7ff7e418126f]
+	(No symbol) [0x0x7ff7e41a968a]
+	(No symbol) [0x0x7ff7e4181003]
+	(No symbol) [0x0x7ff7e41495d1]
+	(No symbol) [0x0x7ff7e414a3f3]
+	GetHandleVerifier [0x0x7ff7e463dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7e4637fca+2936586]
+	GetHandleVerifier [0x0x7ff7e4658a07+3070279]
+	GetHandleVerifier [0x0x7ff7e439843e+185214]
+	GetHandleVerifier [0x0x7ff7e439fe8f+216527]
+	GetHandleVerifier [0x0x7ff7e4387b94+117460]
+	GetHandleVerifier [0x0x7ff7e4387d4f+117903]
+	GetHandleVerifier [0x0x7ff7e436dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7391ae955+80021]
-	GetHandleVerifier [0x0x7ff7391ae9b0+80112]
-	(No symbol) [0x0x7ff738f3060f]
-	(No symbol) [0x0x7ff738f88854]
-	(No symbol) [0x0x7ff738f88b1c]
-	(No symbol) [0x0x7ff738fdc927]
-	(No symbol) [0x0x7ff738fb126f]
-	(No symbol) [0x0x7ff738fd968a]
-	(No symbol) [0x0x7ff738fb1003]
-	(No symbol) [0x0x7ff738f795d1]
-	(No symbol) [0x0x7ff738f7a3f3]
-	GetHandleVerifier [0x0x7ff73946dd0d+2960461]
-	GetHandleVerifier [0x0x7ff739467fca+2936586]
-	GetHandleVerifier [0x0x7ff739488a07+3070279]
-	GetHandleVerifier [0x0x7ff7391c843e+185214]
-	GetHandleVerifier [0x0x7ff7391cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7391b7b94+117460]
-	GetHandleVerifier [0x0x7ff7391b7d4f+117903]
-	GetHandleVerifier [0x0x7ff73919dc28+11112]
+	GetHandleVerifier [0x0x7ff7e437e955+80021]
+	GetHandleVerifier [0x0x7ff7e437e9b0+80112]
+	(No symbol) [0x0x7ff7e410060f]
+	(No symbol) [0x0x7ff7e4158854]
+	(No symbol) [0x0x7ff7e4158b1c]
+	(No symbol) [0x0x7ff7e41ac927]
+	(No symbol) [0x0x7ff7e418126f]
+	(No symbol) [0x0x7ff7e41a968a]
+	(No symbol) [0x0x7ff7e4181003]
+	(No symbol) [0x0x7ff7e41495d1]
+	(No symbol) [0x0x7ff7e414a3f3]
+	GetHandleVerifier [0x0x7ff7e463dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7e4637fca+2936586]
+	GetHandleVerifier [0x0x7ff7e4658a07+3070279]
+	GetHandleVerifier [0x0x7ff7e439843e+185214]
+	GetHandleVerifier [0x0x7ff7e439fe8f+216527]
+	GetHandleVerifier [0x0x7ff7e4387b94+117460]
+	GetHandleVerifier [0x0x7ff7e4387d4f+117903]
+	GetHandleVerifier [0x0x7ff7e436dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>£34.99</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.tradeinsulations.co.uk/product/110mm-celotex/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7391ae955+80021]
-	GetHandleVerifier [0x0x7ff7391ae9b0+80112]
-	(No symbol) [0x0x7ff738f3060f]
-	(No symbol) [0x0x7ff738f88854]
-	(No symbol) [0x0x7ff738f88b1c]
-	(No symbol) [0x0x7ff738fdc927]
-	(No symbol) [0x0x7ff738fb126f]
-	(No symbol) [0x0x7ff738fd968a]
-	(No symbol) [0x0x7ff738fb1003]
-	(No symbol) [0x0x7ff738f795d1]
-	(No symbol) [0x0x7ff738f7a3f3]
-	GetHandleVerifier [0x0x7ff73946dd0d+2960461]
-	GetHandleVerifier [0x0x7ff739467fca+2936586]
-	GetHandleVerifier [0x0x7ff739488a07+3070279]
-	GetHandleVerifier [0x0x7ff7391c843e+185214]
-	GetHandleVerifier [0x0x7ff7391cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7391b7b94+117460]
-	GetHandleVerifier [0x0x7ff7391b7d4f+117903]
-	GetHandleVerifier [0x0x7ff73919dc28+11112]
+	GetHandleVerifier [0x0x7ff7e437e955+80021]
+	GetHandleVerifier [0x0x7ff7e437e9b0+80112]
+	(No symbol) [0x0x7ff7e410060f]
+	(No symbol) [0x0x7ff7e4158854]
+	(No symbol) [0x0x7ff7e4158b1c]
+	(No symbol) [0x0x7ff7e41ac927]
+	(No symbol) [0x0x7ff7e418126f]
+	(No symbol) [0x0x7ff7e41a968a]
+	(No symbol) [0x0x7ff7e4181003]
+	(No symbol) [0x0x7ff7e41495d1]
+	(No symbol) [0x0x7ff7e414a3f3]
+	GetHandleVerifier [0x0x7ff7e463dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7e4637fca+2936586]
+	GetHandleVerifier [0x0x7ff7e4658a07+3070279]
+	GetHandleVerifier [0x0x7ff7e439843e+185214]
+	GetHandleVerifier [0x0x7ff7e439fe8f+216527]
+	GetHandleVerifier [0x0x7ff7e4387b94+117460]
+	GetHandleVerifier [0x0x7ff7e4387d4f+117903]
+	GetHandleVerifier [0x0x7ff7e436dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7391ae955+80021]
-	GetHandleVerifier [0x0x7ff7391ae9b0+80112]
-	(No symbol) [0x0x7ff738f3060f]
-	(No symbol) [0x0x7ff738f88854]
-	(No symbol) [0x0x7ff738f88b1c]
-	(No symbol) [0x0x7ff738fdc927]
-	(No symbol) [0x0x7ff738fb126f]
-	(No symbol) [0x0x7ff738fd968a]
-	(No symbol) [0x0x7ff738fb1003]
-	(No symbol) [0x0x7ff738f795d1]
-	(No symbol) [0x0x7ff738f7a3f3]
-	GetHandleVerifier [0x0x7ff73946dd0d+2960461]
-	GetHandleVerifier [0x0x7ff739467fca+2936586]
-	GetHandleVerifier [0x0x7ff739488a07+3070279]
-	GetHandleVerifier [0x0x7ff7391c843e+185214]
-	GetHandleVerifier [0x0x7ff7391cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7391b7b94+117460]
-	GetHandleVerifier [0x0x7ff7391b7d4f+117903]
-	GetHandleVerifier [0x0x7ff73919dc28+11112]
+	GetHandleVerifier [0x0x7ff7e437e955+80021]
+	GetHandleVerifier [0x0x7ff7e437e9b0+80112]
+	(No symbol) [0x0x7ff7e410060f]
+	(No symbol) [0x0x7ff7e4158854]
+	(No symbol) [0x0x7ff7e4158b1c]
+	(No symbol) [0x0x7ff7e41ac927]
+	(No symbol) [0x0x7ff7e418126f]
+	(No symbol) [0x0x7ff7e41a968a]
+	(No symbol) [0x0x7ff7e4181003]
+	(No symbol) [0x0x7ff7e41495d1]
+	(No symbol) [0x0x7ff7e414a3f3]
+	GetHandleVerifier [0x0x7ff7e463dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7e4637fca+2936586]
+	GetHandleVerifier [0x0x7ff7e4658a07+3070279]
+	GetHandleVerifier [0x0x7ff7e439843e+185214]
+	GetHandleVerifier [0x0x7ff7e439fe8f+216527]
+	GetHandleVerifier [0x0x7ff7e4387b94+117460]
+	GetHandleVerifier [0x0x7ff7e4387d4f+117903]
+	GetHandleVerifier [0x0x7ff7e436dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Error: 520 Server Error: &lt;none&gt; for url: https://lavaielapelomundo.com/hermanus-garden-route/</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7391ae955+80021]
-	GetHandleVerifier [0x0x7ff7391ae9b0+80112]
-	(No symbol) [0x0x7ff738f3060f]
-	(No symbol) [0x0x7ff738f88854]
-	(No symbol) [0x0x7ff738f88b1c]
-	(No symbol) [0x0x7ff738fdc927]
-	(No symbol) [0x0x7ff738fb126f]
-	(No symbol) [0x0x7ff738fd968a]
-	(No symbol) [0x0x7ff738fb1003]
-	(No symbol) [0x0x7ff738f795d1]
-	(No symbol) [0x0x7ff738f7a3f3]
-	GetHandleVerifier [0x0x7ff73946dd0d+2960461]
-	GetHandleVerifier [0x0x7ff739467fca+2936586]
-	GetHandleVerifier [0x0x7ff739488a07+3070279]
-	GetHandleVerifier [0x0x7ff7391c843e+185214]
-	GetHandleVerifier [0x0x7ff7391cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7391b7b94+117460]
-	GetHandleVerifier [0x0x7ff7391b7d4f+117903]
-	GetHandleVerifier [0x0x7ff73919dc28+11112]
+	GetHandleVerifier [0x0x7ff7e437e955+80021]
+	GetHandleVerifier [0x0x7ff7e437e9b0+80112]
+	(No symbol) [0x0x7ff7e410060f]
+	(No symbol) [0x0x7ff7e4158854]
+	(No symbol) [0x0x7ff7e4158b1c]
+	(No symbol) [0x0x7ff7e41ac927]
+	(No symbol) [0x0x7ff7e418126f]
+	(No symbol) [0x0x7ff7e41a968a]
+	(No symbol) [0x0x7ff7e4181003]
+	(No symbol) [0x0x7ff7e41495d1]
+	(No symbol) [0x0x7ff7e414a3f3]
+	GetHandleVerifier [0x0x7ff7e463dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7e4637fca+2936586]
+	GetHandleVerifier [0x0x7ff7e4658a07+3070279]
+	GetHandleVerifier [0x0x7ff7e439843e+185214]
+	GetHandleVerifier [0x0x7ff7e439fe8f+216527]
+	GetHandleVerifier [0x0x7ff7e4387b94+117460]
+	GetHandleVerifier [0x0x7ff7e4387d4f+117903]
+	GetHandleVerifier [0x0x7ff7e436dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7391ae955+80021]
-	GetHandleVerifier [0x0x7ff7391ae9b0+80112]
-	(No symbol) [0x0x7ff738f3060f]
-	(No symbol) [0x0x7ff738f88854]
-	(No symbol) [0x0x7ff738f88b1c]
-	(No symbol) [0x0x7ff738fdc927]
-	(No symbol) [0x0x7ff738fb126f]
-	(No symbol) [0x0x7ff738fd968a]
-	(No symbol) [0x0x7ff738fb1003]
-	(No symbol) [0x0x7ff738f795d1]
-	(No symbol) [0x0x7ff738f7a3f3]
-	GetHandleVerifier [0x0x7ff73946dd0d+2960461]
-	GetHandleVerifier [0x0x7ff739467fca+2936586]
-	GetHandleVerifier [0x0x7ff739488a07+3070279]
-	GetHandleVerifier [0x0x7ff7391c843e+185214]
-	GetHandleVerifier [0x0x7ff7391cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7391b7b94+117460]
-	GetHandleVerifier [0x0x7ff7391b7d4f+117903]
-	GetHandleVerifier [0x0x7ff73919dc28+11112]
+	GetHandleVerifier [0x0x7ff7e437e955+80021]
+	GetHandleVerifier [0x0x7ff7e437e9b0+80112]
+	(No symbol) [0x0x7ff7e410060f]
+	(No symbol) [0x0x7ff7e4158854]
+	(No symbol) [0x0x7ff7e4158b1c]
+	(No symbol) [0x0x7ff7e41ac927]
+	(No symbol) [0x0x7ff7e418126f]
+	(No symbol) [0x0x7ff7e41a968a]
+	(No symbol) [0x0x7ff7e4181003]
+	(No symbol) [0x0x7ff7e41495d1]
+	(No symbol) [0x0x7ff7e414a3f3]
+	GetHandleVerifier [0x0x7ff7e463dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7e4637fca+2936586]
+	GetHandleVerifier [0x0x7ff7e4658a07+3070279]
+	GetHandleVerifier [0x0x7ff7e439843e+185214]
+	GetHandleVerifier [0x0x7ff7e439fe8f+216527]
+	GetHandleVerifier [0x0x7ff7e4387b94+117460]
+	GetHandleVerifier [0x0x7ff7e4387d4f+117903]
+	GetHandleVerifier [0x0x7ff7e436dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7391ae955+80021]
-	GetHandleVerifier [0x0x7ff7391ae9b0+80112]
-	(No symbol) [0x0x7ff738f3060f]
-	(No symbol) [0x0x7ff738f88854]
-	(No symbol) [0x0x7ff738f88b1c]
-	(No symbol) [0x0x7ff738fdc927]
-	(No symbol) [0x0x7ff738fb126f]
-	(No symbol) [0x0x7ff738fd968a]
-	(No symbol) [0x0x7ff738fb1003]
-	(No symbol) [0x0x7ff738f795d1]
-	(No symbol) [0x0x7ff738f7a3f3]
-	GetHandleVerifier [0x0x7ff73946dd0d+2960461]
-	GetHandleVerifier [0x0x7ff739467fca+2936586]
-	GetHandleVerifier [0x0x7ff739488a07+3070279]
-	GetHandleVerifier [0x0x7ff7391c843e+185214]
-	GetHandleVerifier [0x0x7ff7391cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7391b7b94+117460]
-	GetHandleVerifier [0x0x7ff7391b7d4f+117903]
-	GetHandleVerifier [0x0x7ff73919dc28+11112]
+	GetHandleVerifier [0x0x7ff7e437e955+80021]
+	GetHandleVerifier [0x0x7ff7e437e9b0+80112]
+	(No symbol) [0x0x7ff7e410060f]
+	(No symbol) [0x0x7ff7e4158854]
+	(No symbol) [0x0x7ff7e4158b1c]
+	(No symbol) [0x0x7ff7e41ac927]
+	(No symbol) [0x0x7ff7e418126f]
+	(No symbol) [0x0x7ff7e41a968a]
+	(No symbol) [0x0x7ff7e4181003]
+	(No symbol) [0x0x7ff7e41495d1]
+	(No symbol) [0x0x7ff7e414a3f3]
+	GetHandleVerifier [0x0x7ff7e463dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7e4637fca+2936586]
+	GetHandleVerifier [0x0x7ff7e4658a07+3070279]
+	GetHandleVerifier [0x0x7ff7e439843e+185214]
+	GetHandleVerifier [0x0x7ff7e439fe8f+216527]
+	GetHandleVerifier [0x0x7ff7e4387b94+117460]
+	GetHandleVerifier [0x0x7ff7e4387d4f+117903]
+	GetHandleVerifier [0x0x7ff7e436dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7391ae955+80021]
-	GetHandleVerifier [0x0x7ff7391ae9b0+80112]
-	(No symbol) [0x0x7ff738f3060f]
-	(No symbol) [0x0x7ff738f88854]
-	(No symbol) [0x0x7ff738f88b1c]
-	(No symbol) [0x0x7ff738fdc927]
-	(No symbol) [0x0x7ff738fb126f]
-	(No symbol) [0x0x7ff738fd968a]
-	(No symbol) [0x0x7ff738fb1003]
-	(No symbol) [0x0x7ff738f795d1]
-	(No symbol) [0x0x7ff738f7a3f3]
-	GetHandleVerifier [0x0x7ff73946dd0d+2960461]
-	GetHandleVerifier [0x0x7ff739467fca+2936586]
-	GetHandleVerifier [0x0x7ff739488a07+3070279]
-	GetHandleVerifier [0x0x7ff7391c843e+185214]
-	GetHandleVerifier [0x0x7ff7391cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7391b7b94+117460]
-	GetHandleVerifier [0x0x7ff7391b7d4f+117903]
-	GetHandleVerifier [0x0x7ff73919dc28+11112]
+	GetHandleVerifier [0x0x7ff7e437e955+80021]
+	GetHandleVerifier [0x0x7ff7e437e9b0+80112]
+	(No symbol) [0x0x7ff7e410060f]
+	(No symbol) [0x0x7ff7e4158854]
+	(No symbol) [0x0x7ff7e4158b1c]
+	(No symbol) [0x0x7ff7e41ac927]
+	(No symbol) [0x0x7ff7e418126f]
+	(No symbol) [0x0x7ff7e41a968a]
+	(No symbol) [0x0x7ff7e4181003]
+	(No symbol) [0x0x7ff7e41495d1]
+	(No symbol) [0x0x7ff7e414a3f3]
+	GetHandleVerifier [0x0x7ff7e463dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7e4637fca+2936586]
+	GetHandleVerifier [0x0x7ff7e4658a07+3070279]
+	GetHandleVerifier [0x0x7ff7e439843e+185214]
+	GetHandleVerifier [0x0x7ff7e439fe8f+216527]
+	GetHandleVerifier [0x0x7ff7e4387b94+117460]
+	GetHandleVerifier [0x0x7ff7e4387d4f+117903]
+	GetHandleVerifier [0x0x7ff7e436dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7391ae955+80021]
-	GetHandleVerifier [0x0x7ff7391ae9b0+80112]
-	(No symbol) [0x0x7ff738f3060f]
-	(No symbol) [0x0x7ff738f88854]
-	(No symbol) [0x0x7ff738f88b1c]
-	(No symbol) [0x0x7ff738fdc927]
-	(No symbol) [0x0x7ff738fb126f]
-	(No symbol) [0x0x7ff738fd968a]
-	(No symbol) [0x0x7ff738fb1003]
-	(No symbol) [0x0x7ff738f795d1]
-	(No symbol) [0x0x7ff738f7a3f3]
-	GetHandleVerifier [0x0x7ff73946dd0d+2960461]
-	GetHandleVerifier [0x0x7ff739467fca+2936586]
-	GetHandleVerifier [0x0x7ff739488a07+3070279]
-	GetHandleVerifier [0x0x7ff7391c843e+185214]
-	GetHandleVerifier [0x0x7ff7391cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7391b7b94+117460]
-	GetHandleVerifier [0x0x7ff7391b7d4f+117903]
-	GetHandleVerifier [0x0x7ff73919dc28+11112]
+	GetHandleVerifier [0x0x7ff7e437e955+80021]
+	GetHandleVerifier [0x0x7ff7e437e9b0+80112]
+	(No symbol) [0x0x7ff7e410060f]
+	(No symbol) [0x0x7ff7e4158854]
+	(No symbol) [0x0x7ff7e4158b1c]
+	(No symbol) [0x0x7ff7e41ac927]
+	(No symbol) [0x0x7ff7e418126f]
+	(No symbol) [0x0x7ff7e41a968a]
+	(No symbol) [0x0x7ff7e4181003]
+	(No symbol) [0x0x7ff7e41495d1]
+	(No symbol) [0x0x7ff7e414a3f3]
+	GetHandleVerifier [0x0x7ff7e463dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7e4637fca+2936586]
+	GetHandleVerifier [0x0x7ff7e4658a07+3070279]
+	GetHandleVerifier [0x0x7ff7e439843e+185214]
+	GetHandleVerifier [0x0x7ff7e439fe8f+216527]
+	GetHandleVerifier [0x0x7ff7e4387b94+117460]
+	GetHandleVerifier [0x0x7ff7e4387d4f+117903]
+	GetHandleVerifier [0x0x7ff7e436dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7391ae955+80021]
-	GetHandleVerifier [0x0x7ff7391ae9b0+80112]
-	(No symbol) [0x0x7ff738f3060f]
-	(No symbol) [0x0x7ff738f88854]
-	(No symbol) [0x0x7ff738f88b1c]
-	(No symbol) [0x0x7ff738fdc927]
-	(No symbol) [0x0x7ff738fb126f]
-	(No symbol) [0x0x7ff738fd968a]
-	(No symbol) [0x0x7ff738fb1003]
-	(No symbol) [0x0x7ff738f795d1]
-	(No symbol) [0x0x7ff738f7a3f3]
-	GetHandleVerifier [0x0x7ff73946dd0d+2960461]
-	GetHandleVerifier [0x0x7ff739467fca+2936586]
-	GetHandleVerifier [0x0x7ff739488a07+3070279]
-	GetHandleVerifier [0x0x7ff7391c843e+185214]
-	GetHandleVerifier [0x0x7ff7391cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7391b7b94+117460]
-	GetHandleVerifier [0x0x7ff7391b7d4f+117903]
-	GetHandleVerifier [0x0x7ff73919dc28+11112]
+	GetHandleVerifier [0x0x7ff7e437e955+80021]
+	GetHandleVerifier [0x0x7ff7e437e9b0+80112]
+	(No symbol) [0x0x7ff7e410060f]
+	(No symbol) [0x0x7ff7e4158854]
+	(No symbol) [0x0x7ff7e4158b1c]
+	(No symbol) [0x0x7ff7e41ac927]
+	(No symbol) [0x0x7ff7e418126f]
+	(No symbol) [0x0x7ff7e41a968a]
+	(No symbol) [0x0x7ff7e4181003]
+	(No symbol) [0x0x7ff7e41495d1]
+	(No symbol) [0x0x7ff7e414a3f3]
+	GetHandleVerifier [0x0x7ff7e463dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7e4637fca+2936586]
+	GetHandleVerifier [0x0x7ff7e4658a07+3070279]
+	GetHandleVerifier [0x0x7ff7e439843e+185214]
+	GetHandleVerifier [0x0x7ff7e439fe8f+216527]
+	GetHandleVerifier [0x0x7ff7e4387b94+117460]
+	GetHandleVerifier [0x0x7ff7e4387d4f+117903]
+	GetHandleVerifier [0x0x7ff7e436dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7391ae955+80021]
-	GetHandleVerifier [0x0x7ff7391ae9b0+80112]
-	(No symbol) [0x0x7ff738f3060f]
-	(No symbol) [0x0x7ff738f88854]
-	(No symbol) [0x0x7ff738f88b1c]
-	(No symbol) [0x0x7ff738fdc927]
-	(No symbol) [0x0x7ff738fb126f]
-	(No symbol) [0x0x7ff738fd968a]
-	(No symbol) [0x0x7ff738fb1003]
-	(No symbol) [0x0x7ff738f795d1]
-	(No symbol) [0x0x7ff738f7a3f3]
-	GetHandleVerifier [0x0x7ff73946dd0d+2960461]
-	GetHandleVerifier [0x0x7ff739467fca+2936586]
-	GetHandleVerifier [0x0x7ff739488a07+3070279]
-	GetHandleVerifier [0x0x7ff7391c843e+185214]
-	GetHandleVerifier [0x0x7ff7391cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7391b7b94+117460]
-	GetHandleVerifier [0x0x7ff7391b7d4f+117903]
-	GetHandleVerifier [0x0x7ff73919dc28+11112]
+	GetHandleVerifier [0x0x7ff7e437e955+80021]
+	GetHandleVerifier [0x0x7ff7e437e9b0+80112]
+	(No symbol) [0x0x7ff7e410060f]
+	(No symbol) [0x0x7ff7e4158854]
+	(No symbol) [0x0x7ff7e4158b1c]
+	(No symbol) [0x0x7ff7e41ac927]
+	(No symbol) [0x0x7ff7e418126f]
+	(No symbol) [0x0x7ff7e41a968a]
+	(No symbol) [0x0x7ff7e4181003]
+	(No symbol) [0x0x7ff7e41495d1]
+	(No symbol) [0x0x7ff7e414a3f3]
+	GetHandleVerifier [0x0x7ff7e463dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7e4637fca+2936586]
+	GetHandleVerifier [0x0x7ff7e4658a07+3070279]
+	GetHandleVerifier [0x0x7ff7e439843e+185214]
+	GetHandleVerifier [0x0x7ff7e439fe8f+216527]
+	GetHandleVerifier [0x0x7ff7e4387b94+117460]
+	GetHandleVerifier [0x0x7ff7e4387d4f+117903]
+	GetHandleVerifier [0x0x7ff7e436dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7391ae955+80021]
-	GetHandleVerifier [0x0x7ff7391ae9b0+80112]
-	(No symbol) [0x0x7ff738f3060f]
-	(No symbol) [0x0x7ff738f88854]
-	(No symbol) [0x0x7ff738f88b1c]
-	(No symbol) [0x0x7ff738fdc927]
-	(No symbol) [0x0x7ff738fb126f]
-	(No symbol) [0x0x7ff738fd968a]
-	(No symbol) [0x0x7ff738fb1003]
-	(No symbol) [0x0x7ff738f795d1]
-	(No symbol) [0x0x7ff738f7a3f3]
-	GetHandleVerifier [0x0x7ff73946dd0d+2960461]
-	GetHandleVerifier [0x0x7ff739467fca+2936586]
-	GetHandleVerifier [0x0x7ff739488a07+3070279]
-	GetHandleVerifier [0x0x7ff7391c843e+185214]
-	GetHandleVerifier [0x0x7ff7391cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7391b7b94+117460]
-	GetHandleVerifier [0x0x7ff7391b7d4f+117903]
-	GetHandleVerifier [0x0x7ff73919dc28+11112]
+	GetHandleVerifier [0x0x7ff7e437e955+80021]
+	GetHandleVerifier [0x0x7ff7e437e9b0+80112]
+	(No symbol) [0x0x7ff7e410060f]
+	(No symbol) [0x0x7ff7e4158854]
+	(No symbol) [0x0x7ff7e4158b1c]
+	(No symbol) [0x0x7ff7e41ac927]
+	(No symbol) [0x0x7ff7e418126f]
+	(No symbol) [0x0x7ff7e41a968a]
+	(No symbol) [0x0x7ff7e4181003]
+	(No symbol) [0x0x7ff7e41495d1]
+	(No symbol) [0x0x7ff7e414a3f3]
+	GetHandleVerifier [0x0x7ff7e463dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7e4637fca+2936586]
+	GetHandleVerifier [0x0x7ff7e4658a07+3070279]
+	GetHandleVerifier [0x0x7ff7e439843e+185214]
+	GetHandleVerifier [0x0x7ff7e439fe8f+216527]
+	GetHandleVerifier [0x0x7ff7e4387b94+117460]
+	GetHandleVerifier [0x0x7ff7e4387d4f+117903]
+	GetHandleVerifier [0x0x7ff7e436dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3108,25 +3108,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7391ae955+80021]
-	GetHandleVerifier [0x0x7ff7391ae9b0+80112]
-	(No symbol) [0x0x7ff738f3060f]
-	(No symbol) [0x0x7ff738f88854]
-	(No symbol) [0x0x7ff738f88b1c]
-	(No symbol) [0x0x7ff738fdc927]
-	(No symbol) [0x0x7ff738fb126f]
-	(No symbol) [0x0x7ff738fd968a]
-	(No symbol) [0x0x7ff738fb1003]
-	(No symbol) [0x0x7ff738f795d1]
-	(No symbol) [0x0x7ff738f7a3f3]
-	GetHandleVerifier [0x0x7ff73946dd0d+2960461]
-	GetHandleVerifier [0x0x7ff739467fca+2936586]
-	GetHandleVerifier [0x0x7ff739488a07+3070279]
-	GetHandleVerifier [0x0x7ff7391c843e+185214]
-	GetHandleVerifier [0x0x7ff7391cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7391b7b94+117460]
-	GetHandleVerifier [0x0x7ff7391b7d4f+117903]
-	GetHandleVerifier [0x0x7ff73919dc28+11112]
+	GetHandleVerifier [0x0x7ff7e437e955+80021]
+	GetHandleVerifier [0x0x7ff7e437e9b0+80112]
+	(No symbol) [0x0x7ff7e410060f]
+	(No symbol) [0x0x7ff7e4158854]
+	(No symbol) [0x0x7ff7e4158b1c]
+	(No symbol) [0x0x7ff7e41ac927]
+	(No symbol) [0x0x7ff7e418126f]
+	(No symbol) [0x0x7ff7e41a968a]
+	(No symbol) [0x0x7ff7e4181003]
+	(No symbol) [0x0x7ff7e41495d1]
+	(No symbol) [0x0x7ff7e414a3f3]
+	GetHandleVerifier [0x0x7ff7e463dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7e4637fca+2936586]
+	GetHandleVerifier [0x0x7ff7e4658a07+3070279]
+	GetHandleVerifier [0x0x7ff7e439843e+185214]
+	GetHandleVerifier [0x0x7ff7e439fe8f+216527]
+	GetHandleVerifier [0x0x7ff7e4387b94+117460]
+	GetHandleVerifier [0x0x7ff7e4387d4f+117903]
+	GetHandleVerifier [0x0x7ff7e436dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>£43.90</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.tradeinsulations.co.uk/product/celotex-cw4075-75mm-cavity-wall-board/</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3229,25 +3229,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7391ae955+80021]
-	GetHandleVerifier [0x0x7ff7391ae9b0+80112]
-	(No symbol) [0x0x7ff738f3060f]
-	(No symbol) [0x0x7ff738f88854]
-	(No symbol) [0x0x7ff738f88b1c]
-	(No symbol) [0x0x7ff738fdc927]
-	(No symbol) [0x0x7ff738fb126f]
-	(No symbol) [0x0x7ff738fd968a]
-	(No symbol) [0x0x7ff738fb1003]
-	(No symbol) [0x0x7ff738f795d1]
-	(No symbol) [0x0x7ff738f7a3f3]
-	GetHandleVerifier [0x0x7ff73946dd0d+2960461]
-	GetHandleVerifier [0x0x7ff739467fca+2936586]
-	GetHandleVerifier [0x0x7ff739488a07+3070279]
-	GetHandleVerifier [0x0x7ff7391c843e+185214]
-	GetHandleVerifier [0x0x7ff7391cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7391b7b94+117460]
-	GetHandleVerifier [0x0x7ff7391b7d4f+117903]
-	GetHandleVerifier [0x0x7ff73919dc28+11112]
+	GetHandleVerifier [0x0x7ff7e437e955+80021]
+	GetHandleVerifier [0x0x7ff7e437e9b0+80112]
+	(No symbol) [0x0x7ff7e410060f]
+	(No symbol) [0x0x7ff7e4158854]
+	(No symbol) [0x0x7ff7e4158b1c]
+	(No symbol) [0x0x7ff7e41ac927]
+	(No symbol) [0x0x7ff7e418126f]
+	(No symbol) [0x0x7ff7e41a968a]
+	(No symbol) [0x0x7ff7e4181003]
+	(No symbol) [0x0x7ff7e41495d1]
+	(No symbol) [0x0x7ff7e414a3f3]
+	GetHandleVerifier [0x0x7ff7e463dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7e4637fca+2936586]
+	GetHandleVerifier [0x0x7ff7e4658a07+3070279]
+	GetHandleVerifier [0x0x7ff7e439843e+185214]
+	GetHandleVerifier [0x0x7ff7e439fe8f+216527]
+	GetHandleVerifier [0x0x7ff7e4387b94+117460]
+	GetHandleVerifier [0x0x7ff7e4387d4f+117903]
+	GetHandleVerifier [0x0x7ff7e436dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>£992.06</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.tradeinsulations.co.uk/product/celotex-cw4085-85mm-cavity-wall-board/</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3350,25 +3350,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7391ae955+80021]
-	GetHandleVerifier [0x0x7ff7391ae9b0+80112]
-	(No symbol) [0x0x7ff738f3060f]
-	(No symbol) [0x0x7ff738f88854]
-	(No symbol) [0x0x7ff738f88b1c]
-	(No symbol) [0x0x7ff738fdc927]
-	(No symbol) [0x0x7ff738fb126f]
-	(No symbol) [0x0x7ff738fd968a]
-	(No symbol) [0x0x7ff738fb1003]
-	(No symbol) [0x0x7ff738f795d1]
-	(No symbol) [0x0x7ff738f7a3f3]
-	GetHandleVerifier [0x0x7ff73946dd0d+2960461]
-	GetHandleVerifier [0x0x7ff739467fca+2936586]
-	GetHandleVerifier [0x0x7ff739488a07+3070279]
-	GetHandleVerifier [0x0x7ff7391c843e+185214]
-	GetHandleVerifier [0x0x7ff7391cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7391b7b94+117460]
-	GetHandleVerifier [0x0x7ff7391b7d4f+117903]
-	GetHandleVerifier [0x0x7ff73919dc28+11112]
+	GetHandleVerifier [0x0x7ff7e437e955+80021]
+	GetHandleVerifier [0x0x7ff7e437e9b0+80112]
+	(No symbol) [0x0x7ff7e410060f]
+	(No symbol) [0x0x7ff7e4158854]
+	(No symbol) [0x0x7ff7e4158b1c]
+	(No symbol) [0x0x7ff7e41ac927]
+	(No symbol) [0x0x7ff7e418126f]
+	(No symbol) [0x0x7ff7e41a968a]
+	(No symbol) [0x0x7ff7e4181003]
+	(No symbol) [0x0x7ff7e41495d1]
+	(No symbol) [0x0x7ff7e414a3f3]
+	GetHandleVerifier [0x0x7ff7e463dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7e4637fca+2936586]
+	GetHandleVerifier [0x0x7ff7e4658a07+3070279]
+	GetHandleVerifier [0x0x7ff7e439843e+185214]
+	GetHandleVerifier [0x0x7ff7e439fe8f+216527]
+	GetHandleVerifier [0x0x7ff7e4387b94+117460]
+	GetHandleVerifier [0x0x7ff7e4387d4f+117903]
+	GetHandleVerifier [0x0x7ff7e436dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3471,25 +3471,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7391ae955+80021]
-	GetHandleVerifier [0x0x7ff7391ae9b0+80112]
-	(No symbol) [0x0x7ff738f3060f]
-	(No symbol) [0x0x7ff738f88854]
-	(No symbol) [0x0x7ff738f88b1c]
-	(No symbol) [0x0x7ff738fdc927]
-	(No symbol) [0x0x7ff738fb126f]
-	(No symbol) [0x0x7ff738fd968a]
-	(No symbol) [0x0x7ff738fb1003]
-	(No symbol) [0x0x7ff738f795d1]
-	(No symbol) [0x0x7ff738f7a3f3]
-	GetHandleVerifier [0x0x7ff73946dd0d+2960461]
-	GetHandleVerifier [0x0x7ff739467fca+2936586]
-	GetHandleVerifier [0x0x7ff739488a07+3070279]
-	GetHandleVerifier [0x0x7ff7391c843e+185214]
-	GetHandleVerifier [0x0x7ff7391cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7391b7b94+117460]
-	GetHandleVerifier [0x0x7ff7391b7d4f+117903]
-	GetHandleVerifier [0x0x7ff73919dc28+11112]
+	GetHandleVerifier [0x0x7ff7e437e955+80021]
+	GetHandleVerifier [0x0x7ff7e437e9b0+80112]
+	(No symbol) [0x0x7ff7e410060f]
+	(No symbol) [0x0x7ff7e4158854]
+	(No symbol) [0x0x7ff7e4158b1c]
+	(No symbol) [0x0x7ff7e41ac927]
+	(No symbol) [0x0x7ff7e418126f]
+	(No symbol) [0x0x7ff7e41a968a]
+	(No symbol) [0x0x7ff7e4181003]
+	(No symbol) [0x0x7ff7e41495d1]
+	(No symbol) [0x0x7ff7e414a3f3]
+	GetHandleVerifier [0x0x7ff7e463dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7e4637fca+2936586]
+	GetHandleVerifier [0x0x7ff7e4658a07+3070279]
+	GetHandleVerifier [0x0x7ff7e439843e+185214]
+	GetHandleVerifier [0x0x7ff7e439fe8f+216527]
+	GetHandleVerifier [0x0x7ff7e4387b94+117460]
+	GetHandleVerifier [0x0x7ff7e4387d4f+117903]
+	GetHandleVerifier [0x0x7ff7e436dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
